--- a/tournament.xlsx
+++ b/tournament.xlsx
@@ -9,12 +9,13 @@
     <sheet name="王者決定戦_1" r:id="rId3" sheetId="1"/>
     <sheet name="test_test" r:id="rId4" sheetId="2"/>
     <sheet name="仮トーナメント_Pen4" r:id="rId5" sheetId="3"/>
+    <sheet name="シングルストーナメント_2026092103" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="76">
   <si>
     <t>王者決定戦 (1)</t>
   </si>
@@ -170,6 +171,78 @@
   </si>
   <si>
     <t>第1回戦敗退: EmeraldREX91、pipis_57</t>
+  </si>
+  <si>
+    <t>シングルストーナメント (2026092103)</t>
+  </si>
+  <si>
+    <t>シングルス / 5点2セット制(デュース) / 14人参加</t>
+  </si>
+  <si>
+    <t>TYPE_NOOB</t>
+  </si>
+  <si>
+    <t>Dra_goons</t>
+  </si>
+  <si>
+    <t>Rosario20</t>
+  </si>
+  <si>
+    <t>omarupin</t>
+  </si>
+  <si>
+    <t>M0nJ</t>
+  </si>
+  <si>
+    <t>hachi_18</t>
+  </si>
+  <si>
+    <t>Opanku</t>
+  </si>
+  <si>
+    <t>5-1 5-1</t>
+  </si>
+  <si>
+    <t>6-4 5-3</t>
+  </si>
+  <si>
+    <t>5-3 5-7 5-2</t>
+  </si>
+  <si>
+    <t>6-4 2-5 5-3</t>
+  </si>
+  <si>
+    <t>5-3 7-5</t>
+  </si>
+  <si>
+    <t>第2回戦</t>
+  </si>
+  <si>
+    <t>7-5 5-1</t>
+  </si>
+  <si>
+    <t>5-1 0-5 5-3</t>
+  </si>
+  <si>
+    <t>5-1 5-3</t>
+  </si>
+  <si>
+    <t>6-4 3-5 5-3</t>
+  </si>
+  <si>
+    <t>5-3 5-0</t>
+  </si>
+  <si>
+    <t>5-2 8-6</t>
+  </si>
+  <si>
+    <t>準優勝: sota2486</t>
+  </si>
+  <si>
+    <t>2回戦敗退: TYPE_NOOB、pipis_57、M0nJ、Opanku</t>
+  </si>
+  <si>
+    <t>1回戦敗退: Dra_goons、Rosario20、AndroidA、omarupin、hachi_18、AndroidB</t>
   </si>
 </sst>
 </file>
@@ -177,13 +250,35 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="29">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="10"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -498,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -734,6 +829,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyAlignment="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -1101,14 +1237,14 @@
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.75" customWidth="true"/>
-    <col min="2" max="2" width="11.71875" customWidth="true"/>
-    <col min="3" max="3" width="11.71875" customWidth="true"/>
-    <col min="4" max="4" width="11.71875" customWidth="true"/>
-    <col min="5" max="5" width="11.71875" customWidth="true"/>
-    <col min="6" max="6" width="11.71875" customWidth="true"/>
-    <col min="7" max="7" width="11.71875" customWidth="true"/>
-    <col min="8" max="8" width="18.75" customWidth="true"/>
+    <col min="1" max="1" customWidth="true" width="18.75"/>
+    <col min="2" max="2" customWidth="true" width="11.71875"/>
+    <col min="3" max="3" customWidth="true" width="11.71875"/>
+    <col min="4" max="4" customWidth="true" width="11.71875"/>
+    <col min="5" max="5" customWidth="true" width="11.71875"/>
+    <col min="6" max="6" customWidth="true" width="11.71875"/>
+    <col min="7" max="7" customWidth="true" width="11.71875"/>
+    <col min="8" max="8" customWidth="true" width="18.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1487,4 +1623,716 @@
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:J72"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.75" customWidth="true"/>
+    <col min="2" max="2" width="11.71875" customWidth="true"/>
+    <col min="3" max="3" width="11.71875" customWidth="true"/>
+    <col min="4" max="4" width="11.71875" customWidth="true"/>
+    <col min="5" max="5" width="11.71875" customWidth="true"/>
+    <col min="6" max="6" width="11.71875" customWidth="true"/>
+    <col min="7" max="7" width="11.71875" customWidth="true"/>
+    <col min="8" max="8" width="11.71875" customWidth="true"/>
+    <col min="9" max="9" width="11.71875" customWidth="true"/>
+    <col min="10" max="10" width="18.75" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="150">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="151">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="161"/>
+      <c r="C7" t="n" s="157">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="154"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="161"/>
+      <c r="E8" t="n" s="157">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="159"/>
+      <c r="C9" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="158"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="154"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="161"/>
+      <c r="G10" t="n" s="157">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="161"/>
+      <c r="C11" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="D11" s="160"/>
+      <c r="F11" s="158"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="154"/>
+      <c r="B12" s="158"/>
+      <c r="C12" s="161"/>
+      <c r="D12" s="159"/>
+      <c r="E12" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="158"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="159"/>
+      <c r="C13" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="158"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="154"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="161"/>
+      <c r="H14" s="162"/>
+      <c r="I14" t="n" s="156">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="154" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="161"/>
+      <c r="C15" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="F15" s="160"/>
+      <c r="H15" s="160"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="154"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
+      <c r="E16" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="160"/>
+      <c r="H16" s="160"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="159"/>
+      <c r="C17" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="158"/>
+      <c r="F17" s="160"/>
+      <c r="H17" s="160"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="154"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="159"/>
+      <c r="G18" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="160"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="154" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="162"/>
+      <c r="C19" t="n" s="156">
+        <v>1.0</v>
+      </c>
+      <c r="D19" s="160"/>
+      <c r="H19" s="160"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="154"/>
+      <c r="B20" s="160"/>
+      <c r="C20" s="161"/>
+      <c r="D20" s="159"/>
+      <c r="E20" t="n" s="156">
+        <v>1.0</v>
+      </c>
+      <c r="H20" s="160"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="163"/>
+      <c r="C21" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="H21" s="160"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="154"/>
+      <c r="H22" s="160"/>
+      <c r="I22" s="161"/>
+      <c r="J22" s="155" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="154" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="161"/>
+      <c r="C23" t="n" s="157">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="158"/>
+      <c r="J23" s="155"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="154"/>
+      <c r="B24" s="158"/>
+      <c r="C24" s="161"/>
+      <c r="D24" s="161"/>
+      <c r="E24" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="H24" s="158"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="159"/>
+      <c r="C25" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="D25" s="158"/>
+      <c r="H25" s="158"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="154"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="161"/>
+      <c r="F26" s="161"/>
+      <c r="G26" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="H26" s="158"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="154" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="162"/>
+      <c r="C27" t="n" s="156">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="160"/>
+      <c r="F27" s="158"/>
+      <c r="H27" s="158"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="154"/>
+      <c r="B28" s="160"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="159"/>
+      <c r="E28" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="158"/>
+      <c r="H28" s="158"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="154" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="163"/>
+      <c r="C29" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="F29" s="158"/>
+      <c r="H29" s="158"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="154"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="163"/>
+      <c r="I30" t="n" s="157">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="161"/>
+      <c r="C31" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="F31" s="160"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="154"/>
+      <c r="B32" s="158"/>
+      <c r="C32" s="161"/>
+      <c r="D32" s="161"/>
+      <c r="E32" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="F32" s="160"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="154" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="159"/>
+      <c r="C33" t="n" s="156">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="158"/>
+      <c r="F33" s="160"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="154"/>
+      <c r="D34" s="158"/>
+      <c r="E34" s="161"/>
+      <c r="F34" s="159"/>
+      <c r="G34" t="n" s="156">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="154" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="161"/>
+      <c r="C35" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="D35" s="160"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="154"/>
+      <c r="B36" s="158"/>
+      <c r="C36" s="161"/>
+      <c r="D36" s="159"/>
+      <c r="E36" t="n" s="156">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="154" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="159"/>
+      <c r="C37" t="n" s="156">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="154"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="152">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="154" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="162"/>
+      <c r="C43" t="n" s="156">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="154"/>
+      <c r="B44" s="160"/>
+      <c r="C44" s="161"/>
+      <c r="D44" s="155" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="155"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="163"/>
+      <c r="C45" t="n" s="157">
+        <v>2.0</v>
+      </c>
+      <c r="D45" s="155"/>
+      <c r="E45" s="155"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="154"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="152">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="153">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s" s="153">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s" s="153">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s" s="153">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s" s="153">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s" s="153">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s" s="151">
+        <v>55</v>
+      </c>
+      <c r="D50" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s" s="151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s" s="153">
+        <v>36</v>
+      </c>
+      <c r="C51" t="s" s="151">
+        <v>56</v>
+      </c>
+      <c r="D51" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E51" t="s" s="151">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s" s="153">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s" s="151">
+        <v>30</v>
+      </c>
+      <c r="D52" t="s" s="151">
+        <v>16</v>
+      </c>
+      <c r="E52" t="s" s="151">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B53" t="s" s="153">
+        <v>58</v>
+      </c>
+      <c r="C53" t="s" s="151">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s" s="151">
+        <v>16</v>
+      </c>
+      <c r="E53" t="s" s="151">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s" s="153">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s" s="151">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s" s="151">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="151">
+        <v>40</v>
+      </c>
+      <c r="B55" t="s" s="153">
+        <v>60</v>
+      </c>
+      <c r="C55" t="s" s="151">
+        <v>32</v>
+      </c>
+      <c r="D55" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E55" t="s" s="151">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="151">
+        <v>66</v>
+      </c>
+      <c r="B56" t="s" s="153">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s" s="151">
+        <v>54</v>
+      </c>
+      <c r="D56" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E56" t="s" s="151">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="151">
+        <v>66</v>
+      </c>
+      <c r="B57" t="s" s="153">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s" s="151">
+        <v>35</v>
+      </c>
+      <c r="D57" t="s" s="151">
+        <v>16</v>
+      </c>
+      <c r="E57" t="s" s="151">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="151">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s" s="153">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s" s="151">
+        <v>58</v>
+      </c>
+      <c r="D58" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s" s="151">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="151">
+        <v>66</v>
+      </c>
+      <c r="B59" t="s" s="153">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s" s="151">
+        <v>60</v>
+      </c>
+      <c r="D59" t="s" s="151">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s" s="151">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="151">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s" s="153">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s" s="151">
+        <v>36</v>
+      </c>
+      <c r="D60" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E60" t="s" s="151">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="151">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s" s="153">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s" s="151">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E61" t="s" s="151">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="151">
+        <v>20</v>
+      </c>
+      <c r="B62" t="s" s="153">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s" s="151">
+        <v>3</v>
+      </c>
+      <c r="D62" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s" s="151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="151">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s" s="153">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s" s="151">
+        <v>36</v>
+      </c>
+      <c r="D63" t="s" s="151">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s" s="151">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="152">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="151">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="151">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="151">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="151">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="151">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="151">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="151">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="J22:J23"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="D44:E45"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>